--- a/data/externalStats/File1/RPT_RPT5480410465097TZ_externalStats.xlsx
+++ b/data/externalStats/File1/RPT_RPT5480410465097TZ_externalStats.xlsx
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>5120351.540857111</v>
+        <v>5120351.54085711</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>10663.33630118522</v>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>4981587.952723639</v>
+        <v>4981587.952723638</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>750.8195946421827</v>
@@ -3148,7 +3148,7 @@
         <v>1789465.390993749</v>
       </c>
       <c r="AI39" s="56" t="n">
-        <v>2313.128836677754</v>
+        <v>2313.128836677755</v>
       </c>
       <c r="AK39" s="123" t="n">
         <v>15</v>
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>1408907.590304917</v>
+        <v>1408907.590304918</v>
       </c>
       <c r="AI42" s="56" t="n">
         <v>1821.671488505163</v>
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>1286600.071392587</v>
+        <v>1286600.071392588</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>4107.743727999999</v>
@@ -4310,7 +4310,7 @@
         <v>4914</v>
       </c>
       <c r="J58" s="130" t="n">
-        <v>3577.003300060699</v>
+        <v>3577.0033000607</v>
       </c>
       <c r="K58" s="131" t="n">
         <v>1115.559154852213</v>
@@ -4331,7 +4331,7 @@
         <v>1143.041250161384</v>
       </c>
       <c r="R58" s="131" t="n">
-        <v>272.2636155054546</v>
+        <v>272.2636155054545</v>
       </c>
       <c r="S58" s="131" t="n">
         <v>0</v>
@@ -4343,7 +4343,7 @@
         <v>3639.560687871758</v>
       </c>
       <c r="W58" s="131" t="n">
-        <v>1157.115197318205</v>
+        <v>1157.115197318206</v>
       </c>
       <c r="X58" s="131" t="n">
         <v>271.4243920631149</v>
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>1394375.389541362</v>
+        <v>1394375.389541361</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>4568.302288</v>
@@ -4397,10 +4397,10 @@
         <v>0</v>
       </c>
       <c r="L59" s="131" t="n">
-        <v>356.0046394393262</v>
+        <v>356.0046394393264</v>
       </c>
       <c r="M59" s="131" t="n">
-        <v>3624.967623118619</v>
+        <v>3624.96762311862</v>
       </c>
       <c r="N59" s="132" t="n">
         <v>3980.972262557946</v>
@@ -4415,7 +4415,7 @@
         <v>399.0857002490135</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>3984.019885597682</v>
+        <v>3984.019885597681</v>
       </c>
       <c r="T59" s="132" t="n">
         <v>4383.105585846695</v>
@@ -4430,10 +4430,10 @@
         <v>449.3890492690073</v>
       </c>
       <c r="Y59" s="131" t="n">
-        <v>4399.047859818669</v>
+        <v>4399.047859818668</v>
       </c>
       <c r="Z59" s="132" t="n">
-        <v>4848.436909087676</v>
+        <v>4848.436909087675</v>
       </c>
       <c r="AE59" s="121" t="n">
         <v>11</v>
@@ -4586,13 +4586,13 @@
         <v>3030.200510783199</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>802.7197261091694</v>
+        <v>802.7197261091698</v>
       </c>
       <c r="X61" s="131" t="n">
         <v>266.1453571552707</v>
       </c>
       <c r="Y61" s="131" t="n">
-        <v>427.7866374611582</v>
+        <v>427.7866374611581</v>
       </c>
       <c r="Z61" s="132" t="n">
         <v>4526.852231508798</v>
@@ -4690,7 +4690,7 @@
         <v>716582.3096759347</v>
       </c>
       <c r="AH62" s="56" t="n">
-        <v>493.6664213250515</v>
+        <v>493.6664213250516</v>
       </c>
     </row>
     <row r="63">
@@ -4718,13 +4718,13 @@
         <v>6063.963028375118</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1028.516213076213</v>
+        <v>1028.516213076212</v>
       </c>
       <c r="L63" s="131" t="n">
         <v>482.4032427834436</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>2644.761445481005</v>
+        <v>2644.761445481003</v>
       </c>
       <c r="N63" s="132" t="n">
         <v>10219.64392971578</v>
@@ -4736,7 +4736,7 @@
         <v>1192.650797495557</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>519.426457454229</v>
+        <v>519.4264574542285</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>2834.005975254689</v>
@@ -4745,19 +4745,19 @@
         <v>11443.31380395808</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>7858.821665971955</v>
+        <v>7858.82166597194</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>1393.143371473849</v>
+        <v>1393.143371473847</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>544.4036228611681</v>
+        <v>544.4036228611694</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>3094.855133886601</v>
+        <v>3094.8551338866</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>12891.22379419357</v>
+        <v>12891.22379419356</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -4820,10 +4820,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>2406.657072991981</v>
+        <v>2406.65707299198</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>2406.657072991981</v>
+        <v>2406.65707299198</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -5048,7 +5048,7 @@
         <v>36007.66823156677</v>
       </c>
       <c r="K67" s="140" t="n">
-        <v>5431.185034624419</v>
+        <v>5431.18503462442</v>
       </c>
       <c r="L67" s="140" t="n">
         <v>1643.87665807868</v>
@@ -5072,13 +5072,13 @@
         <v>1412.269704923372</v>
       </c>
       <c r="T67" s="141" t="n">
-        <v>41574.56348066354</v>
+        <v>41574.56348066353</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>33426.99961360798</v>
+        <v>33426.99961360799</v>
       </c>
       <c r="W67" s="140" t="n">
-        <v>4250.604456183504</v>
+        <v>4250.604456183505</v>
       </c>
       <c r="X67" s="140" t="n">
         <v>1375.045066978046</v>
@@ -5087,7 +5087,7 @@
         <v>1620.213936787498</v>
       </c>
       <c r="Z67" s="141" t="n">
-        <v>40672.86307355703</v>
+        <v>40672.86307355704</v>
       </c>
       <c r="AE67" s="121" t="n">
         <v>19</v>
@@ -5135,7 +5135,7 @@
         <v>2999.721861871521</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>8039.032327282991</v>
+        <v>8039.03232728299</v>
       </c>
       <c r="N68" s="144" t="n">
         <v>69996.87349981786</v>
@@ -5150,10 +5150,10 @@
         <v>2910.660891075922</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>8643.219611259963</v>
+        <v>8643.219611259961</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>69165.54395418754</v>
+        <v>69165.54395418752</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>47955.58247823489</v>
@@ -5162,13 +5162,13 @@
         <v>7603.582751084728</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>2906.407488326607</v>
+        <v>2906.407488326608</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>9541.903567953927</v>
+        <v>9541.903567953925</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>70624.80683457617</v>
+        <v>70624.80683457616</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -5686,7 +5686,7 @@
         <v>183.3258960552939</v>
       </c>
       <c r="P76" s="130" t="n">
-        <v>131.730420890442</v>
+        <v>131.7304208904419</v>
       </c>
       <c r="Q76" s="131" t="n">
         <v>44.13363173601853</v>
@@ -5698,13 +5698,13 @@
         <v>0</v>
       </c>
       <c r="T76" s="132" t="n">
-        <v>188.3115226657953</v>
+        <v>188.3115226657952</v>
       </c>
       <c r="V76" s="130" t="n">
         <v>134.3980143349047</v>
       </c>
       <c r="W76" s="131" t="n">
-        <v>45.05511271165162</v>
+        <v>45.05511271165161</v>
       </c>
       <c r="X76" s="131" t="n">
         <v>12.70713982589314</v>
@@ -5759,7 +5759,7 @@
         <v>0</v>
       </c>
       <c r="R77" s="131" t="n">
-        <v>51.03944690346368</v>
+        <v>51.03944690346369</v>
       </c>
       <c r="S77" s="131" t="n">
         <v>346.9012428180422</v>
@@ -5774,7 +5774,7 @@
         <v>0</v>
       </c>
       <c r="X77" s="131" t="n">
-        <v>55.91397637446342</v>
+        <v>55.91397637446341</v>
       </c>
       <c r="Y77" s="131" t="n">
         <v>429.6897602068633</v>
@@ -5887,19 +5887,19 @@
         <v>2866.74538671823</v>
       </c>
       <c r="P79" s="130" t="n">
-        <v>2967.764433241744</v>
+        <v>2967.764433241742</v>
       </c>
       <c r="Q79" s="131" t="n">
         <v>141.3285338860519</v>
       </c>
       <c r="R79" s="131" t="n">
-        <v>62.88054748548264</v>
+        <v>62.88054748548265</v>
       </c>
       <c r="S79" s="131" t="n">
-        <v>7.015569293869918</v>
+        <v>7.015569293869917</v>
       </c>
       <c r="T79" s="132" t="n">
-        <v>3178.989083907148</v>
+        <v>3178.989083907146</v>
       </c>
       <c r="V79" s="130" t="n">
         <v>3244.985982181511</v>
@@ -6284,7 +6284,7 @@
         <v>251057.4170218582</v>
       </c>
       <c r="L85" s="140" t="n">
-        <v>57266.91038557484</v>
+        <v>57266.91038557485</v>
       </c>
       <c r="M85" s="140" t="n">
         <v>969.9340240824499</v>
@@ -6302,7 +6302,7 @@
         <v>57819.37211079454</v>
       </c>
       <c r="S85" s="140" t="n">
-        <v>1095.643510353989</v>
+        <v>1095.64351035399</v>
       </c>
       <c r="T85" s="141" t="n">
         <v>1427459.890486019</v>
@@ -6369,7 +6369,7 @@
         <v>58164.31294237665</v>
       </c>
       <c r="S86" s="143" t="n">
-        <v>1712.189478048318</v>
+        <v>1712.189478048319</v>
       </c>
       <c r="T86" s="144" t="n">
         <v>1433231.575897299</v>
@@ -6882,13 +6882,13 @@
         <v>1158.49513537689</v>
       </c>
       <c r="L94" s="131" t="n">
-        <v>283.833184169213</v>
+        <v>283.8331841692129</v>
       </c>
       <c r="M94" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N94" s="132" t="n">
-        <v>5147.611637068602</v>
+        <v>5147.611637068601</v>
       </c>
       <c r="P94" s="130" t="n">
         <v>3750.11606866504</v>
@@ -6897,7 +6897,7 @@
         <v>1187.174881897403</v>
       </c>
       <c r="R94" s="131" t="n">
-        <v>284.7110855447894</v>
+        <v>284.7110855447893</v>
       </c>
       <c r="S94" s="131" t="n">
         <v>0</v>
@@ -6909,7 +6909,7 @@
         <v>3773.958702206662</v>
       </c>
       <c r="W94" s="131" t="n">
-        <v>1202.170310029857</v>
+        <v>1202.170310029858</v>
       </c>
       <c r="X94" s="131" t="n">
         <v>284.131531889008</v>
@@ -6918,7 +6918,7 @@
         <v>0</v>
       </c>
       <c r="Z94" s="132" t="n">
-        <v>5260.260544125527</v>
+        <v>5260.260544125528</v>
       </c>
     </row>
     <row r="95">
@@ -6949,7 +6949,7 @@
         <v>0</v>
       </c>
       <c r="L95" s="131" t="n">
-        <v>402.7734026265692</v>
+        <v>402.7734026265693</v>
       </c>
       <c r="M95" s="131" t="n">
         <v>3918.426842886723</v>
@@ -6967,10 +6967,10 @@
         <v>450.1251471524772</v>
       </c>
       <c r="S95" s="131" t="n">
-        <v>4330.921128415725</v>
+        <v>4330.921128415724</v>
       </c>
       <c r="T95" s="132" t="n">
-        <v>4781.046275568202</v>
+        <v>4781.046275568201</v>
       </c>
       <c r="V95" s="130" t="n">
         <v>0</v>
@@ -6982,10 +6982,10 @@
         <v>505.3030256434707</v>
       </c>
       <c r="Y95" s="131" t="n">
-        <v>4828.737620025532</v>
+        <v>4828.737620025531</v>
       </c>
       <c r="Z95" s="132" t="n">
-        <v>5334.040645669003</v>
+        <v>5334.040645669002</v>
       </c>
     </row>
     <row r="96">
@@ -7092,7 +7092,7 @@
         <v>6990.874165228501</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>5864.503315119102</v>
+        <v>5864.5033151191</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>899.8761975097224</v>
@@ -7104,13 +7104,13 @@
         <v>419.9396147780896</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>7503.202581192952</v>
+        <v>7503.202581192951</v>
       </c>
       <c r="V97" s="130" t="n">
         <v>6275.186492964711</v>
       </c>
       <c r="W97" s="131" t="n">
-        <v>973.6157956560974</v>
+        <v>973.6157956560976</v>
       </c>
       <c r="X97" s="131" t="n">
         <v>339.1504439813352</v>
@@ -7217,13 +7217,13 @@
         <v>1194.238994803804</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>679.7738238167512</v>
+        <v>679.773823816744</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>2820.790535647194</v>
+        <v>2820.790535647191</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>11796.44714627976</v>
+        <v>11796.44714627975</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>7987.932145193452</v>
@@ -7235,7 +7235,7 @@
         <v>737.999824608065</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>3096.635130837105</v>
+        <v>3096.635130837104</v>
       </c>
       <c r="T99" s="132" t="n">
         <v>13187.12876336129</v>
@@ -7250,7 +7250,7 @@
         <v>801.4714782190786</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>3441.763121139207</v>
+        <v>3441.763121139208</v>
       </c>
       <c r="Z99" s="132" t="n">
         <v>14821.73831296549</v>
@@ -7302,10 +7302,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>2669.286228574398</v>
+        <v>2669.286228574397</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>2669.286228574398</v>
+        <v>2669.286228574397</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -7317,10 +7317,10 @@
         <v>0</v>
       </c>
       <c r="Y100" s="134" t="n">
-        <v>2964.238536228617</v>
+        <v>2964.238536228616</v>
       </c>
       <c r="Z100" s="135" t="n">
-        <v>2964.238536228617</v>
+        <v>2964.238536228616</v>
       </c>
     </row>
     <row r="101">
@@ -7489,7 +7489,7 @@
         <v>256488.6020564826</v>
       </c>
       <c r="L103" s="140" t="n">
-        <v>58910.78704365352</v>
+        <v>58910.78704365353</v>
       </c>
       <c r="M103" s="140" t="n">
         <v>2332.244873956298</v>
@@ -7507,7 +7507,7 @@
         <v>59283.25432236121</v>
       </c>
       <c r="S103" s="140" t="n">
-        <v>2507.913215277361</v>
+        <v>2507.913215277362</v>
       </c>
       <c r="T103" s="141" t="n">
         <v>1469034.453966682</v>
@@ -7556,10 +7556,10 @@
         <v>259663.6372678849</v>
       </c>
       <c r="L104" s="143" t="n">
-        <v>60574.09037739906</v>
+        <v>60574.09037739907</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>9485.151648762694</v>
+        <v>9485.151648762692</v>
       </c>
       <c r="N104" s="144" t="n">
         <v>1488486.609473718</v>
@@ -9224,7 +9224,7 @@
         <v>5329025.207125468</v>
       </c>
       <c r="AI33" s="56" t="n">
-        <v>765.0549989487084</v>
+        <v>765.0549989487085</v>
       </c>
       <c r="AK33" s="123" t="n">
         <v>9</v>
@@ -9301,7 +9301,7 @@
         <v>4048908.72842178</v>
       </c>
       <c r="AI34" s="56" t="n">
-        <v>13973.95203328434</v>
+        <v>13973.95203328433</v>
       </c>
       <c r="AK34" s="123" t="n">
         <v>10</v>
@@ -9669,7 +9669,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>1812297.191199682</v>
+        <v>1812297.191199683</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>5750.8412192</v>
@@ -9739,7 +9739,7 @@
         <v>1751703.99415768</v>
       </c>
       <c r="AI40" s="56" t="n">
-        <v>2220.603683210644</v>
+        <v>2220.603683210645</v>
       </c>
       <c r="AK40" s="123" t="n">
         <v>16</v>
@@ -10404,7 +10404,7 @@
         <v>9220815.753906673</v>
       </c>
       <c r="AH52" s="56" t="n">
-        <v>4451.741441899039</v>
+        <v>4451.741441899038</v>
       </c>
     </row>
     <row r="53">
@@ -10725,7 +10725,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>2441379.112228565</v>
+        <v>2441379.112228566</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>340.0826958485881</v>
@@ -10834,7 +10834,7 @@
         <v>4914</v>
       </c>
       <c r="J58" s="130" t="n">
-        <v>3577.003300060699</v>
+        <v>3577.0033000607</v>
       </c>
       <c r="K58" s="131" t="n">
         <v>1115.559154852213</v>
@@ -10855,7 +10855,7 @@
         <v>1143.041250161384</v>
       </c>
       <c r="R58" s="131" t="n">
-        <v>272.2636155054546</v>
+        <v>272.2636155054545</v>
       </c>
       <c r="S58" s="131" t="n">
         <v>0</v>
@@ -10867,7 +10867,7 @@
         <v>3639.560687871758</v>
       </c>
       <c r="W58" s="131" t="n">
-        <v>1157.115197318205</v>
+        <v>1157.115197318206</v>
       </c>
       <c r="X58" s="131" t="n">
         <v>271.4243920631149</v>
@@ -10921,10 +10921,10 @@
         <v>0</v>
       </c>
       <c r="L59" s="131" t="n">
-        <v>356.0046394393262</v>
+        <v>356.0046394393264</v>
       </c>
       <c r="M59" s="131" t="n">
-        <v>3624.967623118619</v>
+        <v>3624.96762311862</v>
       </c>
       <c r="N59" s="132" t="n">
         <v>3980.972262557946</v>
@@ -10939,7 +10939,7 @@
         <v>399.0857002490135</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>3984.019885597682</v>
+        <v>3984.019885597681</v>
       </c>
       <c r="T59" s="132" t="n">
         <v>4383.105585846695</v>
@@ -10954,10 +10954,10 @@
         <v>449.3890492690073</v>
       </c>
       <c r="Y59" s="131" t="n">
-        <v>4399.047859818669</v>
+        <v>4399.047859818668</v>
       </c>
       <c r="Z59" s="132" t="n">
-        <v>4848.436909087676</v>
+        <v>4848.436909087675</v>
       </c>
       <c r="AE59" s="121" t="n">
         <v>11</v>
@@ -11110,13 +11110,13 @@
         <v>3030.200510783199</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>802.7197261091694</v>
+        <v>802.7197261091698</v>
       </c>
       <c r="X61" s="131" t="n">
         <v>266.1453571552707</v>
       </c>
       <c r="Y61" s="131" t="n">
-        <v>427.7866374611582</v>
+        <v>427.7866374611581</v>
       </c>
       <c r="Z61" s="132" t="n">
         <v>4526.852231508798</v>
@@ -11242,13 +11242,13 @@
         <v>6063.963028375118</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1028.516213076213</v>
+        <v>1028.516213076212</v>
       </c>
       <c r="L63" s="131" t="n">
         <v>482.4032427834436</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>2644.761445481005</v>
+        <v>2644.761445481003</v>
       </c>
       <c r="N63" s="132" t="n">
         <v>10219.64392971578</v>
@@ -11260,7 +11260,7 @@
         <v>1192.650797495557</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>519.426457454229</v>
+        <v>519.4264574542285</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>2834.005975254689</v>
@@ -11269,19 +11269,19 @@
         <v>11443.31380395808</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>7858.821665971955</v>
+        <v>7858.82166597194</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>1393.143371473849</v>
+        <v>1393.143371473847</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>544.4036228611681</v>
+        <v>544.4036228611694</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>3094.855133886601</v>
+        <v>3094.8551338866</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>12891.22379419357</v>
+        <v>12891.22379419356</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -11292,7 +11292,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>638383.8403829136</v>
+        <v>638383.8403829137</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>215.2831138527744</v>
@@ -11344,10 +11344,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>2406.657072991981</v>
+        <v>2406.65707299198</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>2406.657072991981</v>
+        <v>2406.65707299198</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -11572,7 +11572,7 @@
         <v>36007.66823156677</v>
       </c>
       <c r="K67" s="140" t="n">
-        <v>5431.185034624419</v>
+        <v>5431.18503462442</v>
       </c>
       <c r="L67" s="140" t="n">
         <v>1643.87665807868</v>
@@ -11596,13 +11596,13 @@
         <v>1412.269704923372</v>
       </c>
       <c r="T67" s="141" t="n">
-        <v>41574.56348066354</v>
+        <v>41574.56348066353</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>33426.99961360798</v>
+        <v>33426.99961360799</v>
       </c>
       <c r="W67" s="140" t="n">
-        <v>4250.604456183504</v>
+        <v>4250.604456183505</v>
       </c>
       <c r="X67" s="140" t="n">
         <v>1375.045066978046</v>
@@ -11611,7 +11611,7 @@
         <v>1620.213936787498</v>
       </c>
       <c r="Z67" s="141" t="n">
-        <v>40672.86307355703</v>
+        <v>40672.86307355704</v>
       </c>
       <c r="AE67" s="121" t="n">
         <v>19</v>
@@ -11622,7 +11622,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>361226.993722062</v>
+        <v>361226.9937220621</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>739.6117635636783</v>
@@ -11659,7 +11659,7 @@
         <v>2999.721861871521</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>8039.032327282991</v>
+        <v>8039.03232728299</v>
       </c>
       <c r="N68" s="144" t="n">
         <v>69996.87349981786</v>
@@ -11674,10 +11674,10 @@
         <v>2910.660891075922</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>8643.219611259963</v>
+        <v>8643.219611259961</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>69165.54395418754</v>
+        <v>69165.54395418752</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>47955.58247823489</v>
@@ -11686,13 +11686,13 @@
         <v>7603.582751084728</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>2906.407488326607</v>
+        <v>2906.407488326608</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>9541.903567953927</v>
+        <v>9541.903567953925</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>70624.80683457617</v>
+        <v>70624.80683457616</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -11706,7 +11706,7 @@
         <v>311833.8750037245</v>
       </c>
       <c r="AH68" s="84" t="n">
-        <v>924.7472819644801</v>
+        <v>924.7472819644802</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -12210,7 +12210,7 @@
         <v>183.3258960552939</v>
       </c>
       <c r="P76" s="130" t="n">
-        <v>131.730420890442</v>
+        <v>131.7304208904419</v>
       </c>
       <c r="Q76" s="131" t="n">
         <v>44.13363173601853</v>
@@ -12222,13 +12222,13 @@
         <v>0</v>
       </c>
       <c r="T76" s="132" t="n">
-        <v>188.3115226657953</v>
+        <v>188.3115226657952</v>
       </c>
       <c r="V76" s="130" t="n">
         <v>134.3980143349047</v>
       </c>
       <c r="W76" s="131" t="n">
-        <v>45.05511271165162</v>
+        <v>45.05511271165161</v>
       </c>
       <c r="X76" s="131" t="n">
         <v>12.70713982589314</v>
@@ -12283,7 +12283,7 @@
         <v>0</v>
       </c>
       <c r="R77" s="131" t="n">
-        <v>51.03944690346368</v>
+        <v>51.03944690346369</v>
       </c>
       <c r="S77" s="131" t="n">
         <v>346.9012428180422</v>
@@ -12298,7 +12298,7 @@
         <v>0</v>
       </c>
       <c r="X77" s="131" t="n">
-        <v>55.91397637446342</v>
+        <v>55.91397637446341</v>
       </c>
       <c r="Y77" s="131" t="n">
         <v>429.6897602068633</v>
@@ -12411,19 +12411,19 @@
         <v>2866.74538671823</v>
       </c>
       <c r="P79" s="130" t="n">
-        <v>2967.764433241744</v>
+        <v>2967.764433241742</v>
       </c>
       <c r="Q79" s="131" t="n">
         <v>141.3285338860519</v>
       </c>
       <c r="R79" s="131" t="n">
-        <v>62.88054748548264</v>
+        <v>62.88054748548265</v>
       </c>
       <c r="S79" s="131" t="n">
-        <v>7.015569293869918</v>
+        <v>7.015569293869917</v>
       </c>
       <c r="T79" s="132" t="n">
-        <v>3178.989083907148</v>
+        <v>3178.989083907146</v>
       </c>
       <c r="V79" s="130" t="n">
         <v>3244.985982181511</v>
@@ -12808,7 +12808,7 @@
         <v>251057.4170218582</v>
       </c>
       <c r="L85" s="140" t="n">
-        <v>57266.91038557484</v>
+        <v>57266.91038557485</v>
       </c>
       <c r="M85" s="140" t="n">
         <v>969.9340240824499</v>
@@ -12826,7 +12826,7 @@
         <v>57819.37211079454</v>
       </c>
       <c r="S85" s="140" t="n">
-        <v>1095.643510353989</v>
+        <v>1095.64351035399</v>
       </c>
       <c r="T85" s="141" t="n">
         <v>1427459.890486019</v>
@@ -12893,7 +12893,7 @@
         <v>58164.31294237665</v>
       </c>
       <c r="S86" s="143" t="n">
-        <v>1712.189478048318</v>
+        <v>1712.189478048319</v>
       </c>
       <c r="T86" s="144" t="n">
         <v>1433231.575897299</v>
@@ -13406,13 +13406,13 @@
         <v>1158.49513537689</v>
       </c>
       <c r="L94" s="131" t="n">
-        <v>283.833184169213</v>
+        <v>283.8331841692129</v>
       </c>
       <c r="M94" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N94" s="132" t="n">
-        <v>5147.611637068602</v>
+        <v>5147.611637068601</v>
       </c>
       <c r="P94" s="130" t="n">
         <v>3750.11606866504</v>
@@ -13421,7 +13421,7 @@
         <v>1187.174881897403</v>
       </c>
       <c r="R94" s="131" t="n">
-        <v>284.7110855447894</v>
+        <v>284.7110855447893</v>
       </c>
       <c r="S94" s="131" t="n">
         <v>0</v>
@@ -13433,7 +13433,7 @@
         <v>3773.958702206662</v>
       </c>
       <c r="W94" s="131" t="n">
-        <v>1202.170310029857</v>
+        <v>1202.170310029858</v>
       </c>
       <c r="X94" s="131" t="n">
         <v>284.131531889008</v>
@@ -13442,7 +13442,7 @@
         <v>0</v>
       </c>
       <c r="Z94" s="132" t="n">
-        <v>5260.260544125527</v>
+        <v>5260.260544125528</v>
       </c>
     </row>
     <row r="95">
@@ -13473,7 +13473,7 @@
         <v>0</v>
       </c>
       <c r="L95" s="131" t="n">
-        <v>402.7734026265692</v>
+        <v>402.7734026265693</v>
       </c>
       <c r="M95" s="131" t="n">
         <v>3918.426842886723</v>
@@ -13491,10 +13491,10 @@
         <v>450.1251471524772</v>
       </c>
       <c r="S95" s="131" t="n">
-        <v>4330.921128415725</v>
+        <v>4330.921128415724</v>
       </c>
       <c r="T95" s="132" t="n">
-        <v>4781.046275568202</v>
+        <v>4781.046275568201</v>
       </c>
       <c r="V95" s="130" t="n">
         <v>0</v>
@@ -13506,10 +13506,10 @@
         <v>505.3030256434707</v>
       </c>
       <c r="Y95" s="131" t="n">
-        <v>4828.737620025532</v>
+        <v>4828.737620025531</v>
       </c>
       <c r="Z95" s="132" t="n">
-        <v>5334.040645669003</v>
+        <v>5334.040645669002</v>
       </c>
     </row>
     <row r="96">
@@ -13616,7 +13616,7 @@
         <v>6990.874165228501</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>5864.503315119102</v>
+        <v>5864.5033151191</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>899.8761975097224</v>
@@ -13628,13 +13628,13 @@
         <v>419.9396147780896</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>7503.202581192952</v>
+        <v>7503.202581192951</v>
       </c>
       <c r="V97" s="130" t="n">
         <v>6275.186492964711</v>
       </c>
       <c r="W97" s="131" t="n">
-        <v>973.6157956560974</v>
+        <v>973.6157956560976</v>
       </c>
       <c r="X97" s="131" t="n">
         <v>339.1504439813352</v>
@@ -13741,13 +13741,13 @@
         <v>1194.238994803804</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>679.7738238167512</v>
+        <v>679.773823816744</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>2820.790535647194</v>
+        <v>2820.790535647191</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>11796.44714627976</v>
+        <v>11796.44714627975</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>7987.932145193452</v>
@@ -13759,7 +13759,7 @@
         <v>737.999824608065</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>3096.635130837105</v>
+        <v>3096.635130837104</v>
       </c>
       <c r="T99" s="132" t="n">
         <v>13187.12876336129</v>
@@ -13774,7 +13774,7 @@
         <v>801.4714782190786</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>3441.763121139207</v>
+        <v>3441.763121139208</v>
       </c>
       <c r="Z99" s="132" t="n">
         <v>14821.73831296549</v>
@@ -13826,10 +13826,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>2669.286228574398</v>
+        <v>2669.286228574397</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>2669.286228574398</v>
+        <v>2669.286228574397</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -13841,10 +13841,10 @@
         <v>0</v>
       </c>
       <c r="Y100" s="134" t="n">
-        <v>2964.238536228617</v>
+        <v>2964.238536228616</v>
       </c>
       <c r="Z100" s="135" t="n">
-        <v>2964.238536228617</v>
+        <v>2964.238536228616</v>
       </c>
     </row>
     <row r="101">
@@ -14013,7 +14013,7 @@
         <v>256488.6020564826</v>
       </c>
       <c r="L103" s="140" t="n">
-        <v>58910.78704365352</v>
+        <v>58910.78704365353</v>
       </c>
       <c r="M103" s="140" t="n">
         <v>2332.244873956298</v>
@@ -14031,7 +14031,7 @@
         <v>59283.25432236121</v>
       </c>
       <c r="S103" s="140" t="n">
-        <v>2507.913215277361</v>
+        <v>2507.913215277362</v>
       </c>
       <c r="T103" s="141" t="n">
         <v>1469034.453966682</v>
@@ -14080,10 +14080,10 @@
         <v>259663.6372678849</v>
       </c>
       <c r="L104" s="143" t="n">
-        <v>60574.09037739906</v>
+        <v>60574.09037739907</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>9485.151648762694</v>
+        <v>9485.151648762692</v>
       </c>
       <c r="N104" s="144" t="n">
         <v>1488486.609473718</v>
@@ -15152,7 +15152,7 @@
         <v>45235826.03390887</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>57217.44053621581</v>
+        <v>57217.44053621583</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -15822,7 +15822,7 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>4659484.105036949</v>
+        <v>4659484.10503695</v>
       </c>
       <c r="AI34" s="56" t="n">
         <v>15724.71578175682</v>
@@ -16133,7 +16133,7 @@
         <v>2594853.457065148</v>
       </c>
       <c r="AI38" s="56" t="n">
-        <v>8051.177706879998</v>
+        <v>8051.177706879999</v>
       </c>
       <c r="AK38" s="123" t="n">
         <v>14</v>
@@ -16340,7 +16340,7 @@
         <v>1861818.454111506</v>
       </c>
       <c r="AI41" s="56" t="n">
-        <v>3412.859287341889</v>
+        <v>3412.859287341888</v>
       </c>
       <c r="AK41" s="123" t="n">
         <v>17</v>
@@ -16491,7 +16491,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>1738156.812275141</v>
+        <v>1738156.81227514</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>2131.779535882219</v>
@@ -17252,7 +17252,7 @@
         <v>2825067.596067273</v>
       </c>
       <c r="AH56" s="56" t="n">
-        <v>8953.872484479998</v>
+        <v>8953.87248448</v>
       </c>
     </row>
     <row r="57">
@@ -17358,7 +17358,7 @@
         <v>4914</v>
       </c>
       <c r="J58" s="130" t="n">
-        <v>3577.003300060699</v>
+        <v>3577.0033000607</v>
       </c>
       <c r="K58" s="131" t="n">
         <v>1115.559154852213</v>
@@ -17379,7 +17379,7 @@
         <v>1143.041250161384</v>
       </c>
       <c r="R58" s="131" t="n">
-        <v>272.2636155054546</v>
+        <v>272.2636155054545</v>
       </c>
       <c r="S58" s="131" t="n">
         <v>0</v>
@@ -17391,7 +17391,7 @@
         <v>3639.560687871758</v>
       </c>
       <c r="W58" s="131" t="n">
-        <v>1157.115197318205</v>
+        <v>1157.115197318206</v>
       </c>
       <c r="X58" s="131" t="n">
         <v>271.4243920631149</v>
@@ -17445,10 +17445,10 @@
         <v>0</v>
       </c>
       <c r="L59" s="131" t="n">
-        <v>356.0046394393262</v>
+        <v>356.0046394393264</v>
       </c>
       <c r="M59" s="131" t="n">
-        <v>3624.967623118619</v>
+        <v>3624.96762311862</v>
       </c>
       <c r="N59" s="132" t="n">
         <v>3980.972262557946</v>
@@ -17463,7 +17463,7 @@
         <v>399.0857002490135</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>3984.019885597682</v>
+        <v>3984.019885597681</v>
       </c>
       <c r="T59" s="132" t="n">
         <v>4383.105585846695</v>
@@ -17478,10 +17478,10 @@
         <v>449.3890492690073</v>
       </c>
       <c r="Y59" s="131" t="n">
-        <v>4399.047859818669</v>
+        <v>4399.047859818668</v>
       </c>
       <c r="Z59" s="132" t="n">
-        <v>4848.436909087676</v>
+        <v>4848.436909087675</v>
       </c>
       <c r="AE59" s="121" t="n">
         <v>11</v>
@@ -17634,13 +17634,13 @@
         <v>3030.200510783199</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>802.7197261091694</v>
+        <v>802.7197261091698</v>
       </c>
       <c r="X61" s="131" t="n">
         <v>266.1453571552707</v>
       </c>
       <c r="Y61" s="131" t="n">
-        <v>427.7866374611582</v>
+        <v>427.7866374611581</v>
       </c>
       <c r="Z61" s="132" t="n">
         <v>4526.852231508798</v>
@@ -17766,13 +17766,13 @@
         <v>6063.963028375118</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1028.516213076213</v>
+        <v>1028.516213076212</v>
       </c>
       <c r="L63" s="131" t="n">
         <v>482.4032427834436</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>2644.761445481005</v>
+        <v>2644.761445481003</v>
       </c>
       <c r="N63" s="132" t="n">
         <v>10219.64392971578</v>
@@ -17784,7 +17784,7 @@
         <v>1192.650797495557</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>519.426457454229</v>
+        <v>519.4264574542285</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>2834.005975254689</v>
@@ -17793,19 +17793,19 @@
         <v>11443.31380395808</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>7858.821665971955</v>
+        <v>7858.82166597194</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>1393.143371473849</v>
+        <v>1393.143371473847</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>544.4036228611681</v>
+        <v>544.4036228611694</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>3094.855133886601</v>
+        <v>3094.8551338866</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>12891.22379419357</v>
+        <v>12891.22379419356</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -17868,10 +17868,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>2406.657072991981</v>
+        <v>2406.65707299198</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>2406.657072991981</v>
+        <v>2406.65707299198</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -18065,7 +18065,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>440033.7856706332</v>
+        <v>440033.7856706333</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>2097.290874083563</v>
@@ -18096,7 +18096,7 @@
         <v>36007.66823156677</v>
       </c>
       <c r="K67" s="140" t="n">
-        <v>5431.185034624419</v>
+        <v>5431.18503462442</v>
       </c>
       <c r="L67" s="140" t="n">
         <v>1643.87665807868</v>
@@ -18120,13 +18120,13 @@
         <v>1412.269704923372</v>
       </c>
       <c r="T67" s="141" t="n">
-        <v>41574.56348066354</v>
+        <v>41574.56348066353</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>33426.99961360798</v>
+        <v>33426.99961360799</v>
       </c>
       <c r="W67" s="140" t="n">
-        <v>4250.604456183504</v>
+        <v>4250.604456183505</v>
       </c>
       <c r="X67" s="140" t="n">
         <v>1375.045066978046</v>
@@ -18135,7 +18135,7 @@
         <v>1620.213936787498</v>
       </c>
       <c r="Z67" s="141" t="n">
-        <v>40672.86307355703</v>
+        <v>40672.86307355704</v>
       </c>
       <c r="AE67" s="121" t="n">
         <v>19</v>
@@ -18183,7 +18183,7 @@
         <v>2999.721861871521</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>8039.032327282991</v>
+        <v>8039.03232728299</v>
       </c>
       <c r="N68" s="144" t="n">
         <v>69996.87349981786</v>
@@ -18198,10 +18198,10 @@
         <v>2910.660891075922</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>8643.219611259963</v>
+        <v>8643.219611259961</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>69165.54395418754</v>
+        <v>69165.54395418752</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>47955.58247823489</v>
@@ -18210,13 +18210,13 @@
         <v>7603.582751084728</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>2906.407488326607</v>
+        <v>2906.407488326608</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>9541.903567953927</v>
+        <v>9541.903567953925</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>70624.80683457617</v>
+        <v>70624.80683457616</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -18734,7 +18734,7 @@
         <v>183.3258960552939</v>
       </c>
       <c r="P76" s="130" t="n">
-        <v>131.730420890442</v>
+        <v>131.7304208904419</v>
       </c>
       <c r="Q76" s="131" t="n">
         <v>44.13363173601853</v>
@@ -18746,13 +18746,13 @@
         <v>0</v>
       </c>
       <c r="T76" s="132" t="n">
-        <v>188.3115226657953</v>
+        <v>188.3115226657952</v>
       </c>
       <c r="V76" s="130" t="n">
         <v>134.3980143349047</v>
       </c>
       <c r="W76" s="131" t="n">
-        <v>45.05511271165162</v>
+        <v>45.05511271165161</v>
       </c>
       <c r="X76" s="131" t="n">
         <v>12.70713982589314</v>
@@ -18807,7 +18807,7 @@
         <v>0</v>
       </c>
       <c r="R77" s="131" t="n">
-        <v>51.03944690346368</v>
+        <v>51.03944690346369</v>
       </c>
       <c r="S77" s="131" t="n">
         <v>346.9012428180422</v>
@@ -18822,7 +18822,7 @@
         <v>0</v>
       </c>
       <c r="X77" s="131" t="n">
-        <v>55.91397637446342</v>
+        <v>55.91397637446341</v>
       </c>
       <c r="Y77" s="131" t="n">
         <v>429.6897602068633</v>
@@ -18935,19 +18935,19 @@
         <v>2866.74538671823</v>
       </c>
       <c r="P79" s="130" t="n">
-        <v>2967.764433241744</v>
+        <v>2967.764433241742</v>
       </c>
       <c r="Q79" s="131" t="n">
         <v>141.3285338860519</v>
       </c>
       <c r="R79" s="131" t="n">
-        <v>62.88054748548264</v>
+        <v>62.88054748548265</v>
       </c>
       <c r="S79" s="131" t="n">
-        <v>7.015569293869918</v>
+        <v>7.015569293869917</v>
       </c>
       <c r="T79" s="132" t="n">
-        <v>3178.989083907148</v>
+        <v>3178.989083907146</v>
       </c>
       <c r="V79" s="130" t="n">
         <v>3244.985982181511</v>
@@ -19332,7 +19332,7 @@
         <v>251057.4170218582</v>
       </c>
       <c r="L85" s="140" t="n">
-        <v>57266.91038557484</v>
+        <v>57266.91038557485</v>
       </c>
       <c r="M85" s="140" t="n">
         <v>969.9340240824499</v>
@@ -19350,7 +19350,7 @@
         <v>57819.37211079454</v>
       </c>
       <c r="S85" s="140" t="n">
-        <v>1095.643510353989</v>
+        <v>1095.64351035399</v>
       </c>
       <c r="T85" s="141" t="n">
         <v>1427459.890486019</v>
@@ -19417,7 +19417,7 @@
         <v>58164.31294237665</v>
       </c>
       <c r="S86" s="143" t="n">
-        <v>1712.189478048318</v>
+        <v>1712.189478048319</v>
       </c>
       <c r="T86" s="144" t="n">
         <v>1433231.575897299</v>
@@ -19930,13 +19930,13 @@
         <v>1158.49513537689</v>
       </c>
       <c r="L94" s="131" t="n">
-        <v>283.833184169213</v>
+        <v>283.8331841692129</v>
       </c>
       <c r="M94" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N94" s="132" t="n">
-        <v>5147.611637068602</v>
+        <v>5147.611637068601</v>
       </c>
       <c r="P94" s="130" t="n">
         <v>3750.11606866504</v>
@@ -19945,7 +19945,7 @@
         <v>1187.174881897403</v>
       </c>
       <c r="R94" s="131" t="n">
-        <v>284.7110855447894</v>
+        <v>284.7110855447893</v>
       </c>
       <c r="S94" s="131" t="n">
         <v>0</v>
@@ -19957,7 +19957,7 @@
         <v>3773.958702206662</v>
       </c>
       <c r="W94" s="131" t="n">
-        <v>1202.170310029857</v>
+        <v>1202.170310029858</v>
       </c>
       <c r="X94" s="131" t="n">
         <v>284.131531889008</v>
@@ -19966,7 +19966,7 @@
         <v>0</v>
       </c>
       <c r="Z94" s="132" t="n">
-        <v>5260.260544125527</v>
+        <v>5260.260544125528</v>
       </c>
     </row>
     <row r="95">
@@ -19997,7 +19997,7 @@
         <v>0</v>
       </c>
       <c r="L95" s="131" t="n">
-        <v>402.7734026265692</v>
+        <v>402.7734026265693</v>
       </c>
       <c r="M95" s="131" t="n">
         <v>3918.426842886723</v>
@@ -20015,10 +20015,10 @@
         <v>450.1251471524772</v>
       </c>
       <c r="S95" s="131" t="n">
-        <v>4330.921128415725</v>
+        <v>4330.921128415724</v>
       </c>
       <c r="T95" s="132" t="n">
-        <v>4781.046275568202</v>
+        <v>4781.046275568201</v>
       </c>
       <c r="V95" s="130" t="n">
         <v>0</v>
@@ -20030,10 +20030,10 @@
         <v>505.3030256434707</v>
       </c>
       <c r="Y95" s="131" t="n">
-        <v>4828.737620025532</v>
+        <v>4828.737620025531</v>
       </c>
       <c r="Z95" s="132" t="n">
-        <v>5334.040645669003</v>
+        <v>5334.040645669002</v>
       </c>
     </row>
     <row r="96">
@@ -20140,7 +20140,7 @@
         <v>6990.874165228501</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>5864.503315119102</v>
+        <v>5864.5033151191</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>899.8761975097224</v>
@@ -20152,13 +20152,13 @@
         <v>419.9396147780896</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>7503.202581192952</v>
+        <v>7503.202581192951</v>
       </c>
       <c r="V97" s="130" t="n">
         <v>6275.186492964711</v>
       </c>
       <c r="W97" s="131" t="n">
-        <v>973.6157956560974</v>
+        <v>973.6157956560976</v>
       </c>
       <c r="X97" s="131" t="n">
         <v>339.1504439813352</v>
@@ -20265,13 +20265,13 @@
         <v>1194.238994803804</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>679.7738238167512</v>
+        <v>679.773823816744</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>2820.790535647194</v>
+        <v>2820.790535647191</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>11796.44714627976</v>
+        <v>11796.44714627975</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>7987.932145193452</v>
@@ -20283,7 +20283,7 @@
         <v>737.999824608065</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>3096.635130837105</v>
+        <v>3096.635130837104</v>
       </c>
       <c r="T99" s="132" t="n">
         <v>13187.12876336129</v>
@@ -20298,7 +20298,7 @@
         <v>801.4714782190786</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>3441.763121139207</v>
+        <v>3441.763121139208</v>
       </c>
       <c r="Z99" s="132" t="n">
         <v>14821.73831296549</v>
@@ -20350,10 +20350,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>2669.286228574398</v>
+        <v>2669.286228574397</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>2669.286228574398</v>
+        <v>2669.286228574397</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -20365,10 +20365,10 @@
         <v>0</v>
       </c>
       <c r="Y100" s="134" t="n">
-        <v>2964.238536228617</v>
+        <v>2964.238536228616</v>
       </c>
       <c r="Z100" s="135" t="n">
-        <v>2964.238536228617</v>
+        <v>2964.238536228616</v>
       </c>
     </row>
     <row r="101">
@@ -20537,7 +20537,7 @@
         <v>256488.6020564826</v>
       </c>
       <c r="L103" s="140" t="n">
-        <v>58910.78704365352</v>
+        <v>58910.78704365353</v>
       </c>
       <c r="M103" s="140" t="n">
         <v>2332.244873956298</v>
@@ -20555,7 +20555,7 @@
         <v>59283.25432236121</v>
       </c>
       <c r="S103" s="140" t="n">
-        <v>2507.913215277361</v>
+        <v>2507.913215277362</v>
       </c>
       <c r="T103" s="141" t="n">
         <v>1469034.453966682</v>
@@ -20604,10 +20604,10 @@
         <v>259663.6372678849</v>
       </c>
       <c r="L104" s="143" t="n">
-        <v>60574.09037739906</v>
+        <v>60574.09037739907</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>9485.151648762694</v>
+        <v>9485.151648762692</v>
       </c>
       <c r="N104" s="144" t="n">
         <v>1488486.609473718</v>
@@ -22195,7 +22195,7 @@
         <v>6216688.07726003</v>
       </c>
       <c r="AI32" s="56" t="n">
-        <v>801.3791921122272</v>
+        <v>801.3791921122271</v>
       </c>
       <c r="AK32" s="123" t="n">
         <v>8</v>
@@ -22346,10 +22346,10 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>5310405.842538491</v>
+        <v>5310405.84253849</v>
       </c>
       <c r="AI34" s="56" t="n">
-        <v>17641.43818058407</v>
+        <v>17641.43818058408</v>
       </c>
       <c r="AK34" s="123" t="n">
         <v>10</v>
@@ -22864,7 +22864,7 @@
         <v>2029241.191294712</v>
       </c>
       <c r="AI41" s="56" t="n">
-        <v>3570.123843302601</v>
+        <v>3570.123843302602</v>
       </c>
       <c r="AK41" s="123" t="n">
         <v>17</v>
@@ -22941,7 +22941,7 @@
         <v>1963455.430630518</v>
       </c>
       <c r="AI42" s="56" t="n">
-        <v>2764.956425043126</v>
+        <v>2764.956425043127</v>
       </c>
       <c r="AK42" s="123" t="n">
         <v>18</v>
@@ -23331,7 +23331,7 @@
         <v>14020195.01759961</v>
       </c>
       <c r="AH51" s="56" t="n">
-        <v>6234.154297883467</v>
+        <v>6234.154297883468</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" thickBot="1">
@@ -23530,7 +23530,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>9811324.660349391</v>
+        <v>9811324.66034939</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>23659.13977320257</v>
@@ -23692,7 +23692,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>4215691.858598477</v>
+        <v>4215691.858598478</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>10530.01980578507</v>
@@ -23882,7 +23882,7 @@
         <v>4914</v>
       </c>
       <c r="J58" s="130" t="n">
-        <v>3577.003300060699</v>
+        <v>3577.0033000607</v>
       </c>
       <c r="K58" s="131" t="n">
         <v>1115.559154852213</v>
@@ -23903,7 +23903,7 @@
         <v>1143.041250161384</v>
       </c>
       <c r="R58" s="131" t="n">
-        <v>272.2636155054546</v>
+        <v>272.2636155054545</v>
       </c>
       <c r="S58" s="131" t="n">
         <v>0</v>
@@ -23915,7 +23915,7 @@
         <v>3639.560687871758</v>
       </c>
       <c r="W58" s="131" t="n">
-        <v>1157.115197318205</v>
+        <v>1157.115197318206</v>
       </c>
       <c r="X58" s="131" t="n">
         <v>271.4243920631149</v>
@@ -23969,10 +23969,10 @@
         <v>0</v>
       </c>
       <c r="L59" s="131" t="n">
-        <v>356.0046394393262</v>
+        <v>356.0046394393264</v>
       </c>
       <c r="M59" s="131" t="n">
-        <v>3624.967623118619</v>
+        <v>3624.96762311862</v>
       </c>
       <c r="N59" s="132" t="n">
         <v>3980.972262557946</v>
@@ -23987,7 +23987,7 @@
         <v>399.0857002490135</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>3984.019885597682</v>
+        <v>3984.019885597681</v>
       </c>
       <c r="T59" s="132" t="n">
         <v>4383.105585846695</v>
@@ -24002,10 +24002,10 @@
         <v>449.3890492690073</v>
       </c>
       <c r="Y59" s="131" t="n">
-        <v>4399.047859818669</v>
+        <v>4399.047859818668</v>
       </c>
       <c r="Z59" s="132" t="n">
-        <v>4848.436909087676</v>
+        <v>4848.436909087675</v>
       </c>
       <c r="AE59" s="121" t="n">
         <v>11</v>
@@ -24097,7 +24097,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>906466.4909447691</v>
+        <v>906466.490944769</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>539.0692909435293</v>
@@ -24158,13 +24158,13 @@
         <v>3030.200510783199</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>802.7197261091694</v>
+        <v>802.7197261091698</v>
       </c>
       <c r="X61" s="131" t="n">
         <v>266.1453571552707</v>
       </c>
       <c r="Y61" s="131" t="n">
-        <v>427.7866374611582</v>
+        <v>427.7866374611581</v>
       </c>
       <c r="Z61" s="132" t="n">
         <v>4526.852231508798</v>
@@ -24178,7 +24178,7 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>781605.0418458922</v>
+        <v>781605.0418458923</v>
       </c>
       <c r="AH61" s="56" t="n">
         <v>2348.723611867773</v>
@@ -24290,13 +24290,13 @@
         <v>6063.963028375118</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1028.516213076213</v>
+        <v>1028.516213076212</v>
       </c>
       <c r="L63" s="131" t="n">
         <v>482.4032427834436</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>2644.761445481005</v>
+        <v>2644.761445481003</v>
       </c>
       <c r="N63" s="132" t="n">
         <v>10219.64392971578</v>
@@ -24308,7 +24308,7 @@
         <v>1192.650797495557</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>519.426457454229</v>
+        <v>519.4264574542285</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>2834.005975254689</v>
@@ -24317,19 +24317,19 @@
         <v>11443.31380395808</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>7858.821665971955</v>
+        <v>7858.82166597194</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>1393.143371473849</v>
+        <v>1393.143371473847</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>544.4036228611681</v>
+        <v>544.4036228611694</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>3094.855133886601</v>
+        <v>3094.8551338866</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>12891.22379419357</v>
+        <v>12891.22379419356</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -24392,10 +24392,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>2406.657072991981</v>
+        <v>2406.65707299198</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>2406.657072991981</v>
+        <v>2406.65707299198</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -24620,7 +24620,7 @@
         <v>36007.66823156677</v>
       </c>
       <c r="K67" s="140" t="n">
-        <v>5431.185034624419</v>
+        <v>5431.18503462442</v>
       </c>
       <c r="L67" s="140" t="n">
         <v>1643.87665807868</v>
@@ -24644,13 +24644,13 @@
         <v>1412.269704923372</v>
       </c>
       <c r="T67" s="141" t="n">
-        <v>41574.56348066354</v>
+        <v>41574.56348066353</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>33426.99961360798</v>
+        <v>33426.99961360799</v>
       </c>
       <c r="W67" s="140" t="n">
-        <v>4250.604456183504</v>
+        <v>4250.604456183505</v>
       </c>
       <c r="X67" s="140" t="n">
         <v>1375.045066978046</v>
@@ -24659,7 +24659,7 @@
         <v>1620.213936787498</v>
       </c>
       <c r="Z67" s="141" t="n">
-        <v>40672.86307355703</v>
+        <v>40672.86307355704</v>
       </c>
       <c r="AE67" s="121" t="n">
         <v>19</v>
@@ -24673,7 +24673,7 @@
         <v>334190.0867178393</v>
       </c>
       <c r="AH67" s="56" t="n">
-        <v>913.0841014375313</v>
+        <v>913.0841014375314</v>
       </c>
     </row>
     <row r="68" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -24707,7 +24707,7 @@
         <v>2999.721861871521</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>8039.032327282991</v>
+        <v>8039.03232728299</v>
       </c>
       <c r="N68" s="144" t="n">
         <v>69996.87349981786</v>
@@ -24722,10 +24722,10 @@
         <v>2910.660891075922</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>8643.219611259963</v>
+        <v>8643.219611259961</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>69165.54395418754</v>
+        <v>69165.54395418752</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>47955.58247823489</v>
@@ -24734,13 +24734,13 @@
         <v>7603.582751084728</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>2906.407488326607</v>
+        <v>2906.407488326608</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>9541.903567953927</v>
+        <v>9541.903567953925</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>70624.80683457617</v>
+        <v>70624.80683457616</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -25258,7 +25258,7 @@
         <v>183.3258960552939</v>
       </c>
       <c r="P76" s="130" t="n">
-        <v>131.730420890442</v>
+        <v>131.7304208904419</v>
       </c>
       <c r="Q76" s="131" t="n">
         <v>44.13363173601853</v>
@@ -25270,13 +25270,13 @@
         <v>0</v>
       </c>
       <c r="T76" s="132" t="n">
-        <v>188.3115226657953</v>
+        <v>188.3115226657952</v>
       </c>
       <c r="V76" s="130" t="n">
         <v>134.3980143349047</v>
       </c>
       <c r="W76" s="131" t="n">
-        <v>45.05511271165162</v>
+        <v>45.05511271165161</v>
       </c>
       <c r="X76" s="131" t="n">
         <v>12.70713982589314</v>
@@ -25331,7 +25331,7 @@
         <v>0</v>
       </c>
       <c r="R77" s="131" t="n">
-        <v>51.03944690346368</v>
+        <v>51.03944690346369</v>
       </c>
       <c r="S77" s="131" t="n">
         <v>346.9012428180422</v>
@@ -25346,7 +25346,7 @@
         <v>0</v>
       </c>
       <c r="X77" s="131" t="n">
-        <v>55.91397637446342</v>
+        <v>55.91397637446341</v>
       </c>
       <c r="Y77" s="131" t="n">
         <v>429.6897602068633</v>
@@ -25459,19 +25459,19 @@
         <v>2866.74538671823</v>
       </c>
       <c r="P79" s="130" t="n">
-        <v>2967.764433241744</v>
+        <v>2967.764433241742</v>
       </c>
       <c r="Q79" s="131" t="n">
         <v>141.3285338860519</v>
       </c>
       <c r="R79" s="131" t="n">
-        <v>62.88054748548264</v>
+        <v>62.88054748548265</v>
       </c>
       <c r="S79" s="131" t="n">
-        <v>7.015569293869918</v>
+        <v>7.015569293869917</v>
       </c>
       <c r="T79" s="132" t="n">
-        <v>3178.989083907148</v>
+        <v>3178.989083907146</v>
       </c>
       <c r="V79" s="130" t="n">
         <v>3244.985982181511</v>
@@ -25856,7 +25856,7 @@
         <v>251057.4170218582</v>
       </c>
       <c r="L85" s="140" t="n">
-        <v>57266.91038557484</v>
+        <v>57266.91038557485</v>
       </c>
       <c r="M85" s="140" t="n">
         <v>969.9340240824499</v>
@@ -25874,7 +25874,7 @@
         <v>57819.37211079454</v>
       </c>
       <c r="S85" s="140" t="n">
-        <v>1095.643510353989</v>
+        <v>1095.64351035399</v>
       </c>
       <c r="T85" s="141" t="n">
         <v>1427459.890486019</v>
@@ -25941,7 +25941,7 @@
         <v>58164.31294237665</v>
       </c>
       <c r="S86" s="143" t="n">
-        <v>1712.189478048318</v>
+        <v>1712.189478048319</v>
       </c>
       <c r="T86" s="144" t="n">
         <v>1433231.575897299</v>
@@ -26454,13 +26454,13 @@
         <v>1158.49513537689</v>
       </c>
       <c r="L94" s="131" t="n">
-        <v>283.833184169213</v>
+        <v>283.8331841692129</v>
       </c>
       <c r="M94" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N94" s="132" t="n">
-        <v>5147.611637068602</v>
+        <v>5147.611637068601</v>
       </c>
       <c r="P94" s="130" t="n">
         <v>3750.11606866504</v>
@@ -26469,7 +26469,7 @@
         <v>1187.174881897403</v>
       </c>
       <c r="R94" s="131" t="n">
-        <v>284.7110855447894</v>
+        <v>284.7110855447893</v>
       </c>
       <c r="S94" s="131" t="n">
         <v>0</v>
@@ -26481,7 +26481,7 @@
         <v>3773.958702206662</v>
       </c>
       <c r="W94" s="131" t="n">
-        <v>1202.170310029857</v>
+        <v>1202.170310029858</v>
       </c>
       <c r="X94" s="131" t="n">
         <v>284.131531889008</v>
@@ -26490,7 +26490,7 @@
         <v>0</v>
       </c>
       <c r="Z94" s="132" t="n">
-        <v>5260.260544125527</v>
+        <v>5260.260544125528</v>
       </c>
     </row>
     <row r="95">
@@ -26521,7 +26521,7 @@
         <v>0</v>
       </c>
       <c r="L95" s="131" t="n">
-        <v>402.7734026265692</v>
+        <v>402.7734026265693</v>
       </c>
       <c r="M95" s="131" t="n">
         <v>3918.426842886723</v>
@@ -26539,10 +26539,10 @@
         <v>450.1251471524772</v>
       </c>
       <c r="S95" s="131" t="n">
-        <v>4330.921128415725</v>
+        <v>4330.921128415724</v>
       </c>
       <c r="T95" s="132" t="n">
-        <v>4781.046275568202</v>
+        <v>4781.046275568201</v>
       </c>
       <c r="V95" s="130" t="n">
         <v>0</v>
@@ -26554,10 +26554,10 @@
         <v>505.3030256434707</v>
       </c>
       <c r="Y95" s="131" t="n">
-        <v>4828.737620025532</v>
+        <v>4828.737620025531</v>
       </c>
       <c r="Z95" s="132" t="n">
-        <v>5334.040645669003</v>
+        <v>5334.040645669002</v>
       </c>
     </row>
     <row r="96">
@@ -26664,7 +26664,7 @@
         <v>6990.874165228501</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>5864.503315119102</v>
+        <v>5864.5033151191</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>899.8761975097224</v>
@@ -26676,13 +26676,13 @@
         <v>419.9396147780896</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>7503.202581192952</v>
+        <v>7503.202581192951</v>
       </c>
       <c r="V97" s="130" t="n">
         <v>6275.186492964711</v>
       </c>
       <c r="W97" s="131" t="n">
-        <v>973.6157956560974</v>
+        <v>973.6157956560976</v>
       </c>
       <c r="X97" s="131" t="n">
         <v>339.1504439813352</v>
@@ -26789,13 +26789,13 @@
         <v>1194.238994803804</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>679.7738238167512</v>
+        <v>679.773823816744</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>2820.790535647194</v>
+        <v>2820.790535647191</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>11796.44714627976</v>
+        <v>11796.44714627975</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>7987.932145193452</v>
@@ -26807,7 +26807,7 @@
         <v>737.999824608065</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>3096.635130837105</v>
+        <v>3096.635130837104</v>
       </c>
       <c r="T99" s="132" t="n">
         <v>13187.12876336129</v>
@@ -26822,7 +26822,7 @@
         <v>801.4714782190786</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>3441.763121139207</v>
+        <v>3441.763121139208</v>
       </c>
       <c r="Z99" s="132" t="n">
         <v>14821.73831296549</v>
@@ -26874,10 +26874,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>2669.286228574398</v>
+        <v>2669.286228574397</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>2669.286228574398</v>
+        <v>2669.286228574397</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -26889,10 +26889,10 @@
         <v>0</v>
       </c>
       <c r="Y100" s="134" t="n">
-        <v>2964.238536228617</v>
+        <v>2964.238536228616</v>
       </c>
       <c r="Z100" s="135" t="n">
-        <v>2964.238536228617</v>
+        <v>2964.238536228616</v>
       </c>
     </row>
     <row r="101">
@@ -27061,7 +27061,7 @@
         <v>256488.6020564826</v>
       </c>
       <c r="L103" s="140" t="n">
-        <v>58910.78704365352</v>
+        <v>58910.78704365353</v>
       </c>
       <c r="M103" s="140" t="n">
         <v>2332.244873956298</v>
@@ -27079,7 +27079,7 @@
         <v>59283.25432236121</v>
       </c>
       <c r="S103" s="140" t="n">
-        <v>2507.913215277361</v>
+        <v>2507.913215277362</v>
       </c>
       <c r="T103" s="141" t="n">
         <v>1469034.453966682</v>
@@ -27128,10 +27128,10 @@
         <v>259663.6372678849</v>
       </c>
       <c r="L104" s="143" t="n">
-        <v>60574.09037739906</v>
+        <v>60574.09037739907</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>9485.151648762694</v>
+        <v>9485.151648762692</v>
       </c>
       <c r="N104" s="144" t="n">
         <v>1488486.609473718</v>
@@ -28197,10 +28197,10 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>69285584.18914482</v>
+        <v>69285584.18914481</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>82393.1061648711</v>
+        <v>82393.10616487112</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -28431,7 +28431,7 @@
         <v>17275131.82133583</v>
       </c>
       <c r="AI28" s="56" t="n">
-        <v>1417.4289551095</v>
+        <v>1417.428955109499</v>
       </c>
       <c r="AK28" s="123" t="n">
         <v>4</v>
@@ -28505,7 +28505,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>15478038.23571112</v>
+        <v>15478038.23571111</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>6750.556086456287</v>
@@ -28601,7 +28601,7 @@
         </is>
       </c>
       <c r="AN30" s="58" t="n">
-        <v>556.2605478630086</v>
+        <v>556.2605478630085</v>
       </c>
     </row>
     <row r="31">
@@ -28793,7 +28793,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>6674173.389488898</v>
+        <v>6674173.389488897</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>11760.22606198546</v>
@@ -28950,7 +28950,7 @@
         <v>5298947.526429203</v>
       </c>
       <c r="AI35" s="56" t="n">
-        <v>15780.3083054848</v>
+        <v>15780.30830548479</v>
       </c>
       <c r="AK35" s="123" t="n">
         <v>11</v>
@@ -29385,10 +29385,10 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>2261110.921757243</v>
+        <v>2261110.921757242</v>
       </c>
       <c r="AI41" s="56" t="n">
-        <v>2957.226786839573</v>
+        <v>2957.226786839574</v>
       </c>
       <c r="AK41" s="123" t="n">
         <v>17</v>
@@ -29542,7 +29542,7 @@
         <v>1704572.018423963</v>
       </c>
       <c r="AI43" s="56" t="n">
-        <v>1964.648020269052</v>
+        <v>1964.648020269053</v>
       </c>
       <c r="AK43" s="123" t="n">
         <v>19</v>
@@ -29619,7 +29619,7 @@
         <v>1628208.049291219</v>
       </c>
       <c r="AI44" s="84" t="n">
-        <v>2218.827294049513</v>
+        <v>2218.827294049512</v>
       </c>
       <c r="AK44" s="126" t="n">
         <v>20</v>
@@ -30406,7 +30406,7 @@
         <v>4914</v>
       </c>
       <c r="J58" s="130" t="n">
-        <v>3577.003300060699</v>
+        <v>3577.0033000607</v>
       </c>
       <c r="K58" s="131" t="n">
         <v>1115.559154852213</v>
@@ -30427,7 +30427,7 @@
         <v>1143.041250161384</v>
       </c>
       <c r="R58" s="131" t="n">
-        <v>272.2636155054546</v>
+        <v>272.2636155054545</v>
       </c>
       <c r="S58" s="131" t="n">
         <v>0</v>
@@ -30439,7 +30439,7 @@
         <v>3639.560687871758</v>
       </c>
       <c r="W58" s="131" t="n">
-        <v>1157.115197318205</v>
+        <v>1157.115197318206</v>
       </c>
       <c r="X58" s="131" t="n">
         <v>271.4243920631149</v>
@@ -30493,10 +30493,10 @@
         <v>0</v>
       </c>
       <c r="L59" s="131" t="n">
-        <v>356.0046394393262</v>
+        <v>356.0046394393264</v>
       </c>
       <c r="M59" s="131" t="n">
-        <v>3624.967623118619</v>
+        <v>3624.96762311862</v>
       </c>
       <c r="N59" s="132" t="n">
         <v>3980.972262557946</v>
@@ -30511,7 +30511,7 @@
         <v>399.0857002490135</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>3984.019885597682</v>
+        <v>3984.019885597681</v>
       </c>
       <c r="T59" s="132" t="n">
         <v>4383.105585846695</v>
@@ -30526,10 +30526,10 @@
         <v>449.3890492690073</v>
       </c>
       <c r="Y59" s="131" t="n">
-        <v>4399.047859818669</v>
+        <v>4399.047859818668</v>
       </c>
       <c r="Z59" s="132" t="n">
-        <v>4848.436909087676</v>
+        <v>4848.436909087675</v>
       </c>
       <c r="AE59" s="121" t="n">
         <v>11</v>
@@ -30682,13 +30682,13 @@
         <v>3030.200510783199</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>802.7197261091694</v>
+        <v>802.7197261091698</v>
       </c>
       <c r="X61" s="131" t="n">
         <v>266.1453571552707</v>
       </c>
       <c r="Y61" s="131" t="n">
-        <v>427.7866374611582</v>
+        <v>427.7866374611581</v>
       </c>
       <c r="Z61" s="132" t="n">
         <v>4526.852231508798</v>
@@ -30814,13 +30814,13 @@
         <v>6063.963028375118</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1028.516213076213</v>
+        <v>1028.516213076212</v>
       </c>
       <c r="L63" s="131" t="n">
         <v>482.4032427834436</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>2644.761445481005</v>
+        <v>2644.761445481003</v>
       </c>
       <c r="N63" s="132" t="n">
         <v>10219.64392971578</v>
@@ -30832,7 +30832,7 @@
         <v>1192.650797495557</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>519.426457454229</v>
+        <v>519.4264574542285</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>2834.005975254689</v>
@@ -30841,19 +30841,19 @@
         <v>11443.31380395808</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>7858.821665971955</v>
+        <v>7858.82166597194</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>1393.143371473849</v>
+        <v>1393.143371473847</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>544.4036228611681</v>
+        <v>544.4036228611694</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>3094.855133886601</v>
+        <v>3094.8551338866</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>12891.22379419357</v>
+        <v>12891.22379419356</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -30916,10 +30916,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>2406.657072991981</v>
+        <v>2406.65707299198</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>2406.657072991981</v>
+        <v>2406.65707299198</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -31144,7 +31144,7 @@
         <v>36007.66823156677</v>
       </c>
       <c r="K67" s="140" t="n">
-        <v>5431.185034624419</v>
+        <v>5431.18503462442</v>
       </c>
       <c r="L67" s="140" t="n">
         <v>1643.87665807868</v>
@@ -31168,13 +31168,13 @@
         <v>1412.269704923372</v>
       </c>
       <c r="T67" s="141" t="n">
-        <v>41574.56348066354</v>
+        <v>41574.56348066353</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>33426.99961360798</v>
+        <v>33426.99961360799</v>
       </c>
       <c r="W67" s="140" t="n">
-        <v>4250.604456183504</v>
+        <v>4250.604456183505</v>
       </c>
       <c r="X67" s="140" t="n">
         <v>1375.045066978046</v>
@@ -31183,7 +31183,7 @@
         <v>1620.213936787498</v>
       </c>
       <c r="Z67" s="141" t="n">
-        <v>40672.86307355703</v>
+        <v>40672.86307355704</v>
       </c>
       <c r="AE67" s="121" t="n">
         <v>19</v>
@@ -31231,7 +31231,7 @@
         <v>2999.721861871521</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>8039.032327282991</v>
+        <v>8039.03232728299</v>
       </c>
       <c r="N68" s="144" t="n">
         <v>69996.87349981786</v>
@@ -31246,10 +31246,10 @@
         <v>2910.660891075922</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>8643.219611259963</v>
+        <v>8643.219611259961</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>69165.54395418754</v>
+        <v>69165.54395418752</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>47955.58247823489</v>
@@ -31258,13 +31258,13 @@
         <v>7603.582751084728</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>2906.407488326607</v>
+        <v>2906.407488326608</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>9541.903567953927</v>
+        <v>9541.903567953925</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>70624.80683457617</v>
+        <v>70624.80683457616</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -31782,7 +31782,7 @@
         <v>183.3258960552939</v>
       </c>
       <c r="P76" s="130" t="n">
-        <v>131.730420890442</v>
+        <v>131.7304208904419</v>
       </c>
       <c r="Q76" s="131" t="n">
         <v>44.13363173601853</v>
@@ -31794,13 +31794,13 @@
         <v>0</v>
       </c>
       <c r="T76" s="132" t="n">
-        <v>188.3115226657953</v>
+        <v>188.3115226657952</v>
       </c>
       <c r="V76" s="130" t="n">
         <v>134.3980143349047</v>
       </c>
       <c r="W76" s="131" t="n">
-        <v>45.05511271165162</v>
+        <v>45.05511271165161</v>
       </c>
       <c r="X76" s="131" t="n">
         <v>12.70713982589314</v>
@@ -31855,7 +31855,7 @@
         <v>0</v>
       </c>
       <c r="R77" s="131" t="n">
-        <v>51.03944690346368</v>
+        <v>51.03944690346369</v>
       </c>
       <c r="S77" s="131" t="n">
         <v>346.9012428180422</v>
@@ -31870,7 +31870,7 @@
         <v>0</v>
       </c>
       <c r="X77" s="131" t="n">
-        <v>55.91397637446342</v>
+        <v>55.91397637446341</v>
       </c>
       <c r="Y77" s="131" t="n">
         <v>429.6897602068633</v>
@@ -31983,19 +31983,19 @@
         <v>2866.74538671823</v>
       </c>
       <c r="P79" s="130" t="n">
-        <v>2967.764433241744</v>
+        <v>2967.764433241742</v>
       </c>
       <c r="Q79" s="131" t="n">
         <v>141.3285338860519</v>
       </c>
       <c r="R79" s="131" t="n">
-        <v>62.88054748548264</v>
+        <v>62.88054748548265</v>
       </c>
       <c r="S79" s="131" t="n">
-        <v>7.015569293869918</v>
+        <v>7.015569293869917</v>
       </c>
       <c r="T79" s="132" t="n">
-        <v>3178.989083907148</v>
+        <v>3178.989083907146</v>
       </c>
       <c r="V79" s="130" t="n">
         <v>3244.985982181511</v>
@@ -32380,7 +32380,7 @@
         <v>251057.4170218582</v>
       </c>
       <c r="L85" s="140" t="n">
-        <v>57266.91038557484</v>
+        <v>57266.91038557485</v>
       </c>
       <c r="M85" s="140" t="n">
         <v>969.9340240824499</v>
@@ -32398,7 +32398,7 @@
         <v>57819.37211079454</v>
       </c>
       <c r="S85" s="140" t="n">
-        <v>1095.643510353989</v>
+        <v>1095.64351035399</v>
       </c>
       <c r="T85" s="141" t="n">
         <v>1427459.890486019</v>
@@ -32465,7 +32465,7 @@
         <v>58164.31294237665</v>
       </c>
       <c r="S86" s="143" t="n">
-        <v>1712.189478048318</v>
+        <v>1712.189478048319</v>
       </c>
       <c r="T86" s="144" t="n">
         <v>1433231.575897299</v>
@@ -32978,13 +32978,13 @@
         <v>1158.49513537689</v>
       </c>
       <c r="L94" s="131" t="n">
-        <v>283.833184169213</v>
+        <v>283.8331841692129</v>
       </c>
       <c r="M94" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N94" s="132" t="n">
-        <v>5147.611637068602</v>
+        <v>5147.611637068601</v>
       </c>
       <c r="P94" s="130" t="n">
         <v>3750.11606866504</v>
@@ -32993,7 +32993,7 @@
         <v>1187.174881897403</v>
       </c>
       <c r="R94" s="131" t="n">
-        <v>284.7110855447894</v>
+        <v>284.7110855447893</v>
       </c>
       <c r="S94" s="131" t="n">
         <v>0</v>
@@ -33005,7 +33005,7 @@
         <v>3773.958702206662</v>
       </c>
       <c r="W94" s="131" t="n">
-        <v>1202.170310029857</v>
+        <v>1202.170310029858</v>
       </c>
       <c r="X94" s="131" t="n">
         <v>284.131531889008</v>
@@ -33014,7 +33014,7 @@
         <v>0</v>
       </c>
       <c r="Z94" s="132" t="n">
-        <v>5260.260544125527</v>
+        <v>5260.260544125528</v>
       </c>
     </row>
     <row r="95">
@@ -33045,7 +33045,7 @@
         <v>0</v>
       </c>
       <c r="L95" s="131" t="n">
-        <v>402.7734026265692</v>
+        <v>402.7734026265693</v>
       </c>
       <c r="M95" s="131" t="n">
         <v>3918.426842886723</v>
@@ -33063,10 +33063,10 @@
         <v>450.1251471524772</v>
       </c>
       <c r="S95" s="131" t="n">
-        <v>4330.921128415725</v>
+        <v>4330.921128415724</v>
       </c>
       <c r="T95" s="132" t="n">
-        <v>4781.046275568202</v>
+        <v>4781.046275568201</v>
       </c>
       <c r="V95" s="130" t="n">
         <v>0</v>
@@ -33078,10 +33078,10 @@
         <v>505.3030256434707</v>
       </c>
       <c r="Y95" s="131" t="n">
-        <v>4828.737620025532</v>
+        <v>4828.737620025531</v>
       </c>
       <c r="Z95" s="132" t="n">
-        <v>5334.040645669003</v>
+        <v>5334.040645669002</v>
       </c>
     </row>
     <row r="96">
@@ -33188,7 +33188,7 @@
         <v>6990.874165228501</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>5864.503315119102</v>
+        <v>5864.5033151191</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>899.8761975097224</v>
@@ -33200,13 +33200,13 @@
         <v>419.9396147780896</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>7503.202581192952</v>
+        <v>7503.202581192951</v>
       </c>
       <c r="V97" s="130" t="n">
         <v>6275.186492964711</v>
       </c>
       <c r="W97" s="131" t="n">
-        <v>973.6157956560974</v>
+        <v>973.6157956560976</v>
       </c>
       <c r="X97" s="131" t="n">
         <v>339.1504439813352</v>
@@ -33313,13 +33313,13 @@
         <v>1194.238994803804</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>679.7738238167512</v>
+        <v>679.773823816744</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>2820.790535647194</v>
+        <v>2820.790535647191</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>11796.44714627976</v>
+        <v>11796.44714627975</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>7987.932145193452</v>
@@ -33331,7 +33331,7 @@
         <v>737.999824608065</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>3096.635130837105</v>
+        <v>3096.635130837104</v>
       </c>
       <c r="T99" s="132" t="n">
         <v>13187.12876336129</v>
@@ -33346,7 +33346,7 @@
         <v>801.4714782190786</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>3441.763121139207</v>
+        <v>3441.763121139208</v>
       </c>
       <c r="Z99" s="132" t="n">
         <v>14821.73831296549</v>
@@ -33398,10 +33398,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>2669.286228574398</v>
+        <v>2669.286228574397</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>2669.286228574398</v>
+        <v>2669.286228574397</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -33413,10 +33413,10 @@
         <v>0</v>
       </c>
       <c r="Y100" s="134" t="n">
-        <v>2964.238536228617</v>
+        <v>2964.238536228616</v>
       </c>
       <c r="Z100" s="135" t="n">
-        <v>2964.238536228617</v>
+        <v>2964.238536228616</v>
       </c>
     </row>
     <row r="101">
@@ -33585,7 +33585,7 @@
         <v>256488.6020564826</v>
       </c>
       <c r="L103" s="140" t="n">
-        <v>58910.78704365352</v>
+        <v>58910.78704365353</v>
       </c>
       <c r="M103" s="140" t="n">
         <v>2332.244873956298</v>
@@ -33603,7 +33603,7 @@
         <v>59283.25432236121</v>
       </c>
       <c r="S103" s="140" t="n">
-        <v>2507.913215277361</v>
+        <v>2507.913215277362</v>
       </c>
       <c r="T103" s="141" t="n">
         <v>1469034.453966682</v>
@@ -33652,10 +33652,10 @@
         <v>259663.6372678849</v>
       </c>
       <c r="L104" s="143" t="n">
-        <v>60574.09037739906</v>
+        <v>60574.09037739907</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>9485.151648762694</v>
+        <v>9485.151648762692</v>
       </c>
       <c r="N104" s="144" t="n">
         <v>1488486.609473718</v>
